--- a/docs/_baseline/fish_zero_report.xlsx
+++ b/docs/_baseline/fish_zero_report.xlsx
@@ -1,14 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <bookViews>
-    <workbookView activeTab="3"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="조사개황" state="visible" r:id="rId1"/>
     <sheet sheetId="2" name="출현종" state="visible" r:id="rId2"/>
     <sheet sheetId="3" name="건강성평가(FAI)" state="visible" r:id="rId3"/>
-    <sheet sheetId="4" name="License" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">출현종!$A$3:$J$3</definedName>
@@ -18,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89">
   <si>
     <t>어류 조사결과 — 조사개황</t>
   </si>
@@ -80,7 +76,7 @@
     <t>채집도구</t>
   </si>
   <si>
-    <t>흐름상태</t>
+    <t>흐름상태(채집)</t>
   </si>
   <si>
     <t>하천차수</t>
@@ -119,7 +115,7 @@
     <t>하천형태</t>
   </si>
   <si>
-    <t>흐름상태(서식처)</t>
+    <t>흐름상태(유속)</t>
   </si>
   <si>
     <t>특이사항(조사불가 등)</t>
@@ -285,9 +281,6 @@
   </si>
   <si>
     <t>E</t>
-  </si>
-  <si>
-    <t>Thank you for using version 2026.2.519.80 of Telerik Document Processing Libraries. License validation couldn't run, possibly due to a missing Telerik.Licensing NuGet package reference to BaselineGen. See documentation for setup. Learn more about Telerik Document Processing Libraries licensing https://docs.telerik.com/devtools/document-processing/distribution-and-licensing/license-key</t>
   </si>
 </sst>
 </file>
@@ -295,7 +288,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <b val="false"/>
       <i val="false"/>
@@ -353,15 +346,6 @@
       <color rgb="FFB71C1C"/>
       <name val="맑은 고딕"/>
     </font>
-    <font>
-      <b val="false"/>
-      <i val="false"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -394,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true"/>
     <xf numFmtId="0" fontId="1" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" borderId="0" xfId="0" applyFont="true"/>
@@ -410,7 +394,6 @@
     <xf numFmtId="0" fontId="6" borderId="0" xfId="0" applyFont="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1276,19 +1259,4 @@
   <autoFilter ref="A3:AC4"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
-</worksheet>
 </file>
--- a/docs/_baseline/fish_zero_report.xlsx
+++ b/docs/_baseline/fish_zero_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90">
   <si>
     <t>어류 조사결과 — 조사개황</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>※ 각 M = 산출값→배점(0/6.25/12.5), 합산=FAI총점. 등급 A≥80·B≥60·C≥40·D≥20·E&lt;20.</t>
+  </si>
+  <si>
+    <t>※ 하천차수가 비면 M1·M2·M3·M7 구간표를 고를 수 없어 FAI 를 내지 않는다('하천차수 필요' · 조사불가·출현종 없음 선언 제외).</t>
   </si>
   <si>
     <t>조사일</t>
@@ -934,7 +937,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" bestFit="false" customWidth="true" width="12.8515625" hidden="false" outlineLevel="0"/>
@@ -1033,73 +1036,73 @@
         <v>8</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>21</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AB3" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AC3" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">
@@ -1134,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L4" s="7" t="n">
         <v>0</v>
@@ -1188,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="AC4" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
@@ -1255,6 +1258,39 @@
       <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="2"/>
+      <c r="AC7" s="2"/>
+    </row>
   </sheetData>
   <autoFilter ref="A3:AC4"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
